--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95434</v>
+        <v>95602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95228</v>
+        <v>95396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125365454</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97084</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>233220</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slät rutlungmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Conocephalum conicum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vingnäs, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>356447</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6533999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125365459</v>
+        <v>125365458</v>
       </c>
       <c r="B2" t="n">
-        <v>95602</v>
+        <v>95396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125365458</v>
+        <v>125365459</v>
       </c>
       <c r="B3" t="n">
-        <v>95396</v>
+        <v>95602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125365458</v>
+        <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95396</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125365459</v>
+        <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,12 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97084</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95656</v>
+        <v>95663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95450</v>
+        <v>95457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>97146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95663</v>
+        <v>95666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95457</v>
+        <v>95460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97146</v>
+        <v>97149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95666</v>
+        <v>95670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95460</v>
+        <v>95464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97149</v>
+        <v>97153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125365459</v>
       </c>
       <c r="B2" t="n">
-        <v>95670</v>
+        <v>95671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125365458</v>
       </c>
       <c r="B3" t="n">
-        <v>95464</v>
+        <v>95465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97153</v>
+        <v>97154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97154</v>
+        <v>97156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>97158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30444-2019 artfynd.xlsx
+++ b/artfynd/A 30444-2019 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125365454</v>
       </c>
       <c r="B4" t="n">
-        <v>97158</v>
+        <v>97160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
